--- a/src/pandorafits/formats/level3/level3-extension-types.xlsx
+++ b/src/pandorafits/formats/level3/level3-extension-types.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindseywiser/Desktop/Pandora/pandora-fits-main/src/pandorafits/formats/level3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/level3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C599D39C-E361-FA4E-892C-9BDBA77B2F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B29695-FE68-3A45-B8AC-0EBFCE151BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16560" xr2:uid="{EB5DEA7A-6EA6-EB47-ADDE-1F14967F3A57}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>Type</t>
   </si>
@@ -429,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0233A54-CD3D-E748-8429-D9F5A3904B71}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -491,14 +491,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
